--- a/excels/WeightedIPCRTest.xlsx
+++ b/excels/WeightedIPCRTest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -222,7 +222,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,13 +324,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -486,7 +479,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -587,10 +580,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -599,7 +588,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -664,9 +653,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>848520</xdr:colOff>
+      <xdr:colOff>848160</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>106200</xdr:rowOff>
+      <xdr:rowOff>105840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -680,7 +669,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5549760" y="74160"/>
-          <a:ext cx="608760" cy="574920"/>
+          <a:ext cx="608400" cy="574560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -702,9 +691,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>619200</xdr:colOff>
+      <xdr:colOff>618840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>140040</xdr:rowOff>
+      <xdr:rowOff>139680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -718,7 +707,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8365680" y="74160"/>
-          <a:ext cx="643320" cy="608760"/>
+          <a:ext cx="642960" cy="608400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -914,11 +903,11 @@
   <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="19.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="18.49"/>
   </cols>
   <sheetData>
@@ -1432,24 +1421,24 @@
       <c r="F22" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="26" t="s">
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27" t="s">
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="28" t="s">
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="27" t="s">
         <v>30</v>
       </c>
       <c r="S22" s="23" t="s">
@@ -1463,20 +1452,20 @@
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
       <c r="F23" s="24"/>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="28"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="27"/>
       <c r="S23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1487,49 +1476,49 @@
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="29" t="s">
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="29" t="s">
+      <c r="O24" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="29" t="s">
+      <c r="P24" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="Q24" s="29" t="s">
+      <c r="Q24" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="R24" s="28"/>
+      <c r="R24" s="27"/>
       <c r="S24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
@@ -1555,124 +1544,124 @@
       <c r="S26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
       <c r="J27" s="7"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="7"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
       <c r="J29" s="7"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
       <c r="J30" s="7"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
     </row>
